--- a/src/main/resources/testdata/LoginData.xlsx
+++ b/src/main/resources/testdata/LoginData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="LoginData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>

--- a/src/main/resources/testdata/LoginData.xlsx
+++ b/src/main/resources/testdata/LoginData.xlsx
@@ -16,13 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>standard_user</t>
   </si>
@@ -33,10 +27,25 @@
     <t>locked_out_user</t>
   </si>
   <si>
-    <t>invalid_user</t>
-  </si>
-  <si>
     <t>wrong_password</t>
+  </si>
+  <si>
+    <t>Row</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>ExpectedErrorMessage</t>
+  </si>
+  <si>
+    <t>Epic sadface: Sorry, this user has been locked out.</t>
+  </si>
+  <si>
+    <t>Epic sadface: Username and password do not match any user in this service.</t>
   </si>
 </sst>
 </file>
@@ -80,13 +89,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -382,48 +394,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="26.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="1" max="16384" width="26.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="D2" s="3"/>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:4" ht="30">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
